--- a/report/file.xlsx
+++ b/report/file.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1727">
   <si>
     <t>пп</t>
   </si>
@@ -62,6 +62,15 @@
     <t>8 989 085 6863</t>
   </si>
   <si>
+    <t>Азаренко Любовь Адександровна</t>
+  </si>
+  <si>
+    <t>1951-06-23</t>
+  </si>
+  <si>
+    <t>8 993 006 3532</t>
+  </si>
+  <si>
     <t>Азарова Галина Николаевна</t>
   </si>
   <si>
@@ -134,7 +143,7 @@
     <t>2 950 420 6187</t>
   </si>
   <si>
-    <t>Архинева Вероника Нуратдинова</t>
+    <t>Архинева Вероника Нуратдиновна</t>
   </si>
   <si>
     <t>1967-09-03</t>
@@ -143,6 +152,15 @@
     <t>8 989 162 3231</t>
   </si>
   <si>
+    <t>Астромович Ирина Петровна</t>
+  </si>
+  <si>
+    <t>1959-10-24</t>
+  </si>
+  <si>
+    <t>8 950 892 0852</t>
+  </si>
+  <si>
     <t>Аулова Валентина Николаевна</t>
   </si>
   <si>
@@ -161,6 +179,15 @@
     <t>8 929 567 0070</t>
   </si>
   <si>
+    <t>Афлейтонова Ирина Николаевна</t>
+  </si>
+  <si>
+    <t>1960-03-21</t>
+  </si>
+  <si>
+    <t>8 950 817 8224</t>
+  </si>
+  <si>
     <t>Ахмедова Галина Туйчиевна</t>
   </si>
   <si>
@@ -179,6 +206,15 @@
     <t>8 988 500 0524</t>
   </si>
   <si>
+    <t>Баданова Людмила Николаевна</t>
+  </si>
+  <si>
+    <t>1952-06-12</t>
+  </si>
+  <si>
+    <t>8 918 400 7753</t>
+  </si>
+  <si>
     <t>Байдина Ирина Викторовна</t>
   </si>
   <si>
@@ -302,15 +338,33 @@
     <t>8 982 317 4853</t>
   </si>
   <si>
+    <t>Беккер Светлана Николаевна</t>
+  </si>
+  <si>
+    <t>1964-03-18</t>
+  </si>
+  <si>
+    <t>8 918 614 3288</t>
+  </si>
+  <si>
     <t>Белакина Нина Ивановна</t>
   </si>
   <si>
-    <t>1948-12-13</t>
+    <t>0000-00-00</t>
   </si>
   <si>
     <t>8 995 204 4834</t>
   </si>
   <si>
+    <t>Беликова Людмила Николаевна</t>
+  </si>
+  <si>
+    <t>1955-06-04</t>
+  </si>
+  <si>
+    <t>8 918 603 9136</t>
+  </si>
+  <si>
     <t>Белкина Галина Дмитриевна</t>
   </si>
   <si>
@@ -320,6 +374,15 @@
     <t>8 919 466 7419</t>
   </si>
   <si>
+    <t>Белобородов Сергей Валентинович</t>
+  </si>
+  <si>
+    <t>1957-06-14</t>
+  </si>
+  <si>
+    <t>8 918 909 9767</t>
+  </si>
+  <si>
     <t>Бережной Андрей Валерьевич</t>
   </si>
   <si>
@@ -392,6 +455,15 @@
     <t>8 918 919 7372</t>
   </si>
   <si>
+    <t>Богучарский Сергей Михайлович</t>
+  </si>
+  <si>
+    <t>1953-06-15</t>
+  </si>
+  <si>
+    <t>8 900 296 6367</t>
+  </si>
+  <si>
     <t>Бойкова Любовь Владимировна</t>
   </si>
   <si>
@@ -410,15 +482,6 @@
     <t>8 919 222 5276</t>
   </si>
   <si>
-    <t>Борисов Егор Борисович</t>
-  </si>
-  <si>
-    <t>0000-00-00</t>
-  </si>
-  <si>
-    <t>8 978 228 3407</t>
-  </si>
-  <si>
     <t>Борисова Нина Георгиевна</t>
   </si>
   <si>
@@ -452,6 +515,15 @@
     <t>8 922 122 0454</t>
   </si>
   <si>
+    <t>Братченко Тамара Алексеенко</t>
+  </si>
+  <si>
+    <t>1951-10-07</t>
+  </si>
+  <si>
+    <t>8 938 497 0989</t>
+  </si>
+  <si>
     <t>Бубенина Татьяна Петровна</t>
   </si>
   <si>
@@ -461,6 +533,18 @@
     <t>8 918 919 6455</t>
   </si>
   <si>
+    <t>Букша Ольга Александровна</t>
+  </si>
+  <si>
+    <t>Бурлаков Сергей Леонидович</t>
+  </si>
+  <si>
+    <t>1954-06-03</t>
+  </si>
+  <si>
+    <t>8 953 000 6937</t>
+  </si>
+  <si>
     <t>Буславьева Надежда Петровна</t>
   </si>
   <si>
@@ -518,6 +602,15 @@
     <t>8 914 163 7989</t>
   </si>
   <si>
+    <t>Ваганова Валентина Сергеевна</t>
+  </si>
+  <si>
+    <t>1954-01-15</t>
+  </si>
+  <si>
+    <t>8 988 417 6671</t>
+  </si>
+  <si>
     <t>Валиахметова Бриллиант Абзаловна</t>
   </si>
   <si>
@@ -560,15 +653,6 @@
     <t>1954-03-05</t>
   </si>
   <si>
-    <t>Вишневская Диана Ефимовна</t>
-  </si>
-  <si>
-    <t>1951-04-29</t>
-  </si>
-  <si>
-    <t>8 918 200 2235</t>
-  </si>
-  <si>
     <t>Власенко Людмила Кубелевна</t>
   </si>
   <si>
@@ -605,6 +689,15 @@
     <t>8 918 608 6234</t>
   </si>
   <si>
+    <t>Войтович Наталья Александровна</t>
+  </si>
+  <si>
+    <t>1969-04-09</t>
+  </si>
+  <si>
+    <t>8 916 685 3853</t>
+  </si>
+  <si>
     <t xml:space="preserve">Волкова Ольга Михайловна </t>
   </si>
   <si>
@@ -635,9 +728,18 @@
     <t>8 914 529 8030</t>
   </si>
   <si>
+    <t>Волокитин Юрий Александрович</t>
+  </si>
+  <si>
+    <t>1952-10-06</t>
+  </si>
+  <si>
     <t>Воробьева Наталья Анатольевна</t>
   </si>
   <si>
+    <t>1959-04-21</t>
+  </si>
+  <si>
     <t>8 950 650 2794</t>
   </si>
   <si>
@@ -650,6 +752,15 @@
     <t>8 999 897 1036</t>
   </si>
   <si>
+    <t>Востокова Марина Витальевна</t>
+  </si>
+  <si>
+    <t>1962-10-04</t>
+  </si>
+  <si>
+    <t>8 916 167 4392</t>
+  </si>
+  <si>
     <t>Вяжевич Елена Викторовна</t>
   </si>
   <si>
@@ -758,6 +869,15 @@
     <t>8 912 663 8644</t>
   </si>
   <si>
+    <t>Голдобина Наталья Владимировна</t>
+  </si>
+  <si>
+    <t>1966-09-22</t>
+  </si>
+  <si>
+    <t>8 918 913 4452</t>
+  </si>
+  <si>
     <t>Голева Светлана Владимировна</t>
   </si>
   <si>
@@ -776,13 +896,13 @@
     <t>8 918 402 0311</t>
   </si>
   <si>
-    <t>Головина Любовь Антоновна</t>
-  </si>
-  <si>
-    <t>1945-02-02</t>
-  </si>
-  <si>
-    <t>8 918 181 5938</t>
+    <t>Голубева Татьяна Юрьевна</t>
+  </si>
+  <si>
+    <t>1947-11-21</t>
+  </si>
+  <si>
+    <t>8 931 980 9721</t>
   </si>
   <si>
     <t>Гончаренко Ольга Викторовна</t>
@@ -791,6 +911,15 @@
     <t>8 900 261 7924</t>
   </si>
   <si>
+    <t>Гопкало Валентина Владимировна</t>
+  </si>
+  <si>
+    <t>1958-06-05</t>
+  </si>
+  <si>
+    <t>8 965 482 7073</t>
+  </si>
+  <si>
     <t>Грабовенко Лариса Константиновн</t>
   </si>
   <si>
@@ -800,6 +929,15 @@
     <t>8 966 777 6654</t>
   </si>
   <si>
+    <t>Граф Марина Викторовна</t>
+  </si>
+  <si>
+    <t>1964-09-20</t>
+  </si>
+  <si>
+    <t>8 938 875 1225</t>
+  </si>
+  <si>
     <t>Грачева Зинаида Мефодьевна</t>
   </si>
   <si>
@@ -818,6 +956,15 @@
     <t>8 918 268 0017</t>
   </si>
   <si>
+    <t>Григоренко Вера Витальевна</t>
+  </si>
+  <si>
+    <t>1959-01-20</t>
+  </si>
+  <si>
+    <t>8 914 446 5858</t>
+  </si>
+  <si>
     <t>Григорьев Виктор Николаевич</t>
   </si>
   <si>
@@ -833,6 +980,15 @@
     <t>1961-01-30</t>
   </si>
   <si>
+    <t>Григорьева Лариса Суреновна</t>
+  </si>
+  <si>
+    <t>1962-10-01</t>
+  </si>
+  <si>
+    <t>8 958 632 2268</t>
+  </si>
+  <si>
     <t>Григорян Маринэ Робертовна</t>
   </si>
   <si>
@@ -866,13 +1022,13 @@
     <t>8 924 835 7090</t>
   </si>
   <si>
-    <t>Грушевская Любовь Николаевна</t>
-  </si>
-  <si>
-    <t>1947-02-27</t>
-  </si>
-  <si>
-    <t>8 918 901 8842</t>
+    <t>Губернаторова Мария Алексеевна</t>
+  </si>
+  <si>
+    <t>1955-10-26</t>
+  </si>
+  <si>
+    <t>8 961 502 9615</t>
   </si>
   <si>
     <t>Гудина Татьяна Петровна</t>
@@ -947,6 +1103,15 @@
     <t>8 909 386 9609</t>
   </si>
   <si>
+    <t>Деменкова Светлана Геннадьевна</t>
+  </si>
+  <si>
+    <t>1961-07-19</t>
+  </si>
+  <si>
+    <t>8 918 907 9057</t>
+  </si>
+  <si>
     <t>Демидова Лилия Нерсесовна</t>
   </si>
   <si>
@@ -983,6 +1148,15 @@
     <t>8 951 148 8944</t>
   </si>
   <si>
+    <t>Депелян Надежда Васильевна</t>
+  </si>
+  <si>
+    <t>1955-10-12</t>
+  </si>
+  <si>
+    <t>8 928 852 5726</t>
+  </si>
+  <si>
     <t>Диброва Людмила Кирилловна</t>
   </si>
   <si>
@@ -992,6 +1166,15 @@
     <t>8 918 203 4008</t>
   </si>
   <si>
+    <t>Дмитрова Любовь Васильевна</t>
+  </si>
+  <si>
+    <t>1967-07-22</t>
+  </si>
+  <si>
+    <t>8 964 944 5175</t>
+  </si>
+  <si>
     <t>Добрынина Ирина Анатольевна</t>
   </si>
   <si>
@@ -1043,6 +1226,15 @@
     <t>8 905 852 5689</t>
   </si>
   <si>
+    <t>Дорошенко Зоя Евгеньевна</t>
+  </si>
+  <si>
+    <t>1957-01-22</t>
+  </si>
+  <si>
+    <t>8 991 485 9298</t>
+  </si>
+  <si>
     <t>Дорошенко Надежда Федоровна</t>
   </si>
   <si>
@@ -1052,6 +1244,21 @@
     <t>8 918 304 2349</t>
   </si>
   <si>
+    <t>Дробизова Татьяна Анатольевна</t>
+  </si>
+  <si>
+    <t>8 967 325 3454</t>
+  </si>
+  <si>
+    <t>Дроздецкая Марина Германовна</t>
+  </si>
+  <si>
+    <t>1962-03-31</t>
+  </si>
+  <si>
+    <t>8 918 615 6500</t>
+  </si>
+  <si>
     <t>Дука Валентина Алексеевна</t>
   </si>
   <si>
@@ -1061,6 +1268,15 @@
     <t>8 903 861 1947</t>
   </si>
   <si>
+    <t>Дядич Наталья Владмировна</t>
+  </si>
+  <si>
+    <t>1960-09-17</t>
+  </si>
+  <si>
+    <t>8 950 338 4729</t>
+  </si>
+  <si>
     <t>Евсина Алла Владимировна</t>
   </si>
   <si>
@@ -1070,6 +1286,15 @@
     <t>8 903 044 0333</t>
   </si>
   <si>
+    <t xml:space="preserve">Егорова Валентина Александровна             </t>
+  </si>
+  <si>
+    <t>1950-11-14</t>
+  </si>
+  <si>
+    <t>8 908 545 2457</t>
+  </si>
+  <si>
     <t>Ерофеева Алла Владиславовна</t>
   </si>
   <si>
@@ -1097,15 +1322,6 @@
     <t>-8 914 239 5522</t>
   </si>
   <si>
-    <t>Жабинец Александр Прокофьевич</t>
-  </si>
-  <si>
-    <t>1965-07-27</t>
-  </si>
-  <si>
-    <t>8 918 305 6862</t>
-  </si>
-  <si>
     <t>Жукова Ирина Николаевна</t>
   </si>
   <si>
@@ -1223,6 +1439,15 @@
     <t>8 982 316 1350</t>
   </si>
   <si>
+    <t>Зорик Татьяна Васильевна</t>
+  </si>
+  <si>
+    <t>1951-12-08</t>
+  </si>
+  <si>
+    <t>8 918 443 8516</t>
+  </si>
+  <si>
     <t>Иванова Людмила Вячеславовна</t>
   </si>
   <si>
@@ -1232,6 +1457,15 @@
     <t>8 912 958 0240</t>
   </si>
   <si>
+    <t>Иванова Светлана Павловна</t>
+  </si>
+  <si>
+    <t>1962-01-10</t>
+  </si>
+  <si>
+    <t>8 909 418 6470</t>
+  </si>
+  <si>
     <t>Иванова Татьяна Романовна</t>
   </si>
   <si>
@@ -1283,6 +1517,15 @@
     <t>8 999 657 0989</t>
   </si>
   <si>
+    <t>Ильина Елена Александровна</t>
+  </si>
+  <si>
+    <t>1962-05-06</t>
+  </si>
+  <si>
+    <t>8 926 942 7708</t>
+  </si>
+  <si>
     <t>Исаева Наталья Васильевна</t>
   </si>
   <si>
@@ -1307,6 +1550,15 @@
     <t>8 967 320 1746</t>
   </si>
   <si>
+    <t>Кадинская Татьяна Романовна</t>
+  </si>
+  <si>
+    <t>1954-03-12</t>
+  </si>
+  <si>
+    <t>8 918 206 0470</t>
+  </si>
+  <si>
     <t>Казанцева Луиза Равильевна</t>
   </si>
   <si>
@@ -1343,6 +1595,15 @@
     <t>8 918 402 3159</t>
   </si>
   <si>
+    <t>Капитанская Татьяна Васильевна</t>
+  </si>
+  <si>
+    <t>1961-12-14</t>
+  </si>
+  <si>
+    <t>8 918 307 8863</t>
+  </si>
+  <si>
     <t>Капустян Лилия Витальевна</t>
   </si>
   <si>
@@ -1415,6 +1676,15 @@
     <t>8 905 096 9552</t>
   </si>
   <si>
+    <t>Кесян Инна Николаевна</t>
+  </si>
+  <si>
+    <t>1964-06-07</t>
+  </si>
+  <si>
+    <t>8 928 854 1069</t>
+  </si>
+  <si>
     <t>Кизерова Татьяна Валерьевна</t>
   </si>
   <si>
@@ -1424,15 +1694,6 @@
     <t>8 961 884 3612</t>
   </si>
   <si>
-    <t>Кикешев Николай Иванович</t>
-  </si>
-  <si>
-    <t>1946-03-01</t>
-  </si>
-  <si>
-    <t>8 903 232 7449</t>
-  </si>
-  <si>
     <t>Килин Юрий Михайлович</t>
   </si>
   <si>
@@ -1631,6 +1892,15 @@
     <t>8 988 147 2450</t>
   </si>
   <si>
+    <t>Комарова Галина Павловна</t>
+  </si>
+  <si>
+    <t>1956-01-12</t>
+  </si>
+  <si>
+    <t>8 999 555 9670</t>
+  </si>
+  <si>
     <t>Комарова Наталья Анатольевна</t>
   </si>
   <si>
@@ -1658,7 +1928,7 @@
     <t>8 962 883 2322</t>
   </si>
   <si>
-    <t>Комиссаренко Маргарита Анатольев</t>
+    <t>Комиссаренко Маргарита Анатольевна</t>
   </si>
   <si>
     <t>1967-01-14</t>
@@ -1721,9 +1991,24 @@
     <t>8 999 654 0880</t>
   </si>
   <si>
+    <t>Коротова Ирина Васильевна</t>
+  </si>
+  <si>
+    <t>1962-10-27</t>
+  </si>
+  <si>
+    <t>8 962 889 7228</t>
+  </si>
+  <si>
     <t>Корсакова Н</t>
   </si>
   <si>
+    <t>Коршун Леонид Николаевич</t>
+  </si>
+  <si>
+    <t>1959-08-31</t>
+  </si>
+  <si>
     <t>Косых Наталья Анатольевна</t>
   </si>
   <si>
@@ -1742,6 +2027,15 @@
     <t>8 952 811 0884</t>
   </si>
   <si>
+    <t>Котельникова Людмила Геннадьевна</t>
+  </si>
+  <si>
+    <t>1963-06-06</t>
+  </si>
+  <si>
+    <t>8 938 492 7366</t>
+  </si>
+  <si>
     <t>Котик Галина Авксентьевна</t>
   </si>
   <si>
@@ -1751,6 +2045,18 @@
     <t>8 928 452 6148</t>
   </si>
   <si>
+    <t>Котиков Игорь Львович</t>
+  </si>
+  <si>
+    <t>1957-08-27</t>
+  </si>
+  <si>
+    <t>Котов Анатолий Федорович</t>
+  </si>
+  <si>
+    <t>1948-01-27</t>
+  </si>
+  <si>
     <t>Котрачев Виктор Владимирович</t>
   </si>
   <si>
@@ -1820,6 +2126,15 @@
     <t>1959-04-27</t>
   </si>
   <si>
+    <t>Кренштрем Ия Геральд-Освальдовна</t>
+  </si>
+  <si>
+    <t>1963-02-19</t>
+  </si>
+  <si>
+    <t>8 918 303 9766</t>
+  </si>
+  <si>
     <t>Крехалева Наталья Алексеевна</t>
   </si>
   <si>
@@ -1856,6 +2171,15 @@
     <t>8 965 483 3905</t>
   </si>
   <si>
+    <t>Кузнецова Валентина Михайловна</t>
+  </si>
+  <si>
+    <t>1900-03-11</t>
+  </si>
+  <si>
+    <t>8 912 901 7410</t>
+  </si>
+  <si>
     <t>Кузнецова Ирина Евгеньевна</t>
   </si>
   <si>
@@ -1865,6 +2189,15 @@
     <t>8 921 905 8221</t>
   </si>
   <si>
+    <t>Кузьмина Наталья Васильевна</t>
+  </si>
+  <si>
+    <t>1953-11-13</t>
+  </si>
+  <si>
+    <t>8 996 232 8208</t>
+  </si>
+  <si>
     <t>Куклина Валентина Абросимовна</t>
   </si>
   <si>
@@ -1883,10 +2216,19 @@
     <t>8 989 083 7867</t>
   </si>
   <si>
+    <t>Кулаева Елена Викторовна</t>
+  </si>
+  <si>
+    <t>1968-08-25</t>
+  </si>
+  <si>
+    <t>8 938 420 8038</t>
+  </si>
+  <si>
     <t>Кулакова Галина Петровна</t>
   </si>
   <si>
-    <t>2024-05-26</t>
+    <t>1950-05-26</t>
   </si>
   <si>
     <t>8 902 912 1037</t>
@@ -1904,9 +2246,6 @@
     <t>Кулешова Аэлита Иосифовна</t>
   </si>
   <si>
-    <t>1947-11-21</t>
-  </si>
-  <si>
     <t>8 918 002 1597</t>
   </si>
   <si>
@@ -1928,6 +2267,12 @@
     <t>8 918 307 0411</t>
   </si>
   <si>
+    <t>Кулинич Сергей Андреевич</t>
+  </si>
+  <si>
+    <t>1965-05-25</t>
+  </si>
+  <si>
     <t>Куличихина Валентина Ивановна</t>
   </si>
   <si>
@@ -1955,6 +2300,15 @@
     <t>8 900 001 2794</t>
   </si>
   <si>
+    <t>Куприкова Рабига Ивановна</t>
+  </si>
+  <si>
+    <t>1961-02-28</t>
+  </si>
+  <si>
+    <t>8 932 414 4285</t>
+  </si>
+  <si>
     <t>Курлович Лилия Алексеевна</t>
   </si>
   <si>
@@ -1991,6 +2345,15 @@
     <t>8 988 404 2263</t>
   </si>
   <si>
+    <t>Кучеренко Лариса Николаевна</t>
+  </si>
+  <si>
+    <t>1966-04-17</t>
+  </si>
+  <si>
+    <t>8 918 104 2508</t>
+  </si>
+  <si>
     <t>Кучерянова Татьяна Константинов</t>
   </si>
   <si>
@@ -2018,6 +2381,15 @@
     <t>8 918 900 4321</t>
   </si>
   <si>
+    <t>Лебедева Ирина Николаевна</t>
+  </si>
+  <si>
+    <t>1961-09-01</t>
+  </si>
+  <si>
+    <t>8 988 400 0557</t>
+  </si>
+  <si>
     <t>Лебедева Тамара Федоровна</t>
   </si>
   <si>
@@ -2063,6 +2435,15 @@
     <t>8 988 288 5680</t>
   </si>
   <si>
+    <t>Леоненко Нина Федоровна</t>
+  </si>
+  <si>
+    <t>1959-12-15</t>
+  </si>
+  <si>
+    <t>8 924 300 7130</t>
+  </si>
+  <si>
     <t>Леонова Татьяна Владимировна</t>
   </si>
   <si>
@@ -2072,6 +2453,15 @@
     <t>8 913 307 9914</t>
   </si>
   <si>
+    <t>Литвиненко Ирина Анатольевна</t>
+  </si>
+  <si>
+    <t>1961-05-26</t>
+  </si>
+  <si>
+    <t>8 918 301 5997</t>
+  </si>
+  <si>
     <t>Лобанова Елена Рафаэльевна</t>
   </si>
   <si>
@@ -2081,15 +2471,6 @@
     <t>8 916 944 6981</t>
   </si>
   <si>
-    <t>Лодочникова Светлана Александровна</t>
-  </si>
-  <si>
-    <t>1961-09-01</t>
-  </si>
-  <si>
-    <t>8 921 246 6129</t>
-  </si>
-  <si>
     <t>Лодыгин Сергей Михайлович</t>
   </si>
   <si>
@@ -2108,6 +2489,21 @@
     <t>8 989 750 8212</t>
   </si>
   <si>
+    <t>Лучков Николай Борисович</t>
+  </si>
+  <si>
+    <t>1952-05-01</t>
+  </si>
+  <si>
+    <t>Лучкова Елена Федоровна</t>
+  </si>
+  <si>
+    <t>1947-12-23</t>
+  </si>
+  <si>
+    <t>8 903 000 8769</t>
+  </si>
+  <si>
     <t>Лушникова Вера Емельяновна</t>
   </si>
   <si>
@@ -2144,6 +2540,15 @@
     <t>8 918 109 6064</t>
   </si>
   <si>
+    <t>Макеева Наталья Станиславовна</t>
+  </si>
+  <si>
+    <t>1970-11-01</t>
+  </si>
+  <si>
+    <t>8 918 946 8730</t>
+  </si>
+  <si>
     <t>Максимлюк Галина Алексеевна</t>
   </si>
   <si>
@@ -2168,6 +2573,9 @@
     <t>Малхасян Валентина Александровна</t>
   </si>
   <si>
+    <t>1950-01-05</t>
+  </si>
+  <si>
     <t>8 918 400 0052</t>
   </si>
   <si>
@@ -2189,6 +2597,30 @@
     <t>8 917 383 2913</t>
   </si>
   <si>
+    <t>Мамаева Лариса Генриховна</t>
+  </si>
+  <si>
+    <t>1959-06-20</t>
+  </si>
+  <si>
+    <t>8 952 862 5935</t>
+  </si>
+  <si>
+    <t>Манылова Лариса Никаноровна</t>
+  </si>
+  <si>
+    <t>8 918 603 6062</t>
+  </si>
+  <si>
+    <t>Мареева Надежда Митрофановна</t>
+  </si>
+  <si>
+    <t>1962-01-18</t>
+  </si>
+  <si>
+    <t>8 912 925 6247</t>
+  </si>
+  <si>
     <t>Мартенюк Наталья Ивановна</t>
   </si>
   <si>
@@ -2198,6 +2630,24 @@
     <t>8 988 233 5920</t>
   </si>
   <si>
+    <t>Мартынова Светлана Викторовна</t>
+  </si>
+  <si>
+    <t>1967-03-02</t>
+  </si>
+  <si>
+    <t>8 903 243 1915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Марченко Галина Николаевна </t>
+  </si>
+  <si>
+    <t>1962-11-11</t>
+  </si>
+  <si>
+    <t>8 918 302 3916</t>
+  </si>
+  <si>
     <t>Маслова Нина Ивановна</t>
   </si>
   <si>
@@ -2234,6 +2684,24 @@
     <t>8 988 409 7553</t>
   </si>
   <si>
+    <t>Медведева  Наиля Михайловна</t>
+  </si>
+  <si>
+    <t>1969-02-01</t>
+  </si>
+  <si>
+    <t>8 967 321 6427</t>
+  </si>
+  <si>
+    <t>Медведева Валентина Дмитриевна</t>
+  </si>
+  <si>
+    <t>1947-02-25</t>
+  </si>
+  <si>
+    <t>8 914 661 2574</t>
+  </si>
+  <si>
     <t>Мельникова Галина Александровна</t>
   </si>
   <si>
@@ -2300,7 +2768,7 @@
     <t>Меркулова Людмила Владимировна</t>
   </si>
   <si>
-    <t>1962-08-19</t>
+    <t>1962-07-19</t>
   </si>
   <si>
     <t>8 928 967 8400</t>
@@ -2411,6 +2879,9 @@
     <t>8 918 409 1405</t>
   </si>
   <si>
+    <t>Мишкова Милана Олеговна</t>
+  </si>
+  <si>
     <t>Мозговая Ирина Леонтьевна</t>
   </si>
   <si>
@@ -2462,6 +2933,15 @@
     <t>996 553 524313</t>
   </si>
   <si>
+    <t>Морозова Лариса Викторовна</t>
+  </si>
+  <si>
+    <t>1972-07-22</t>
+  </si>
+  <si>
+    <t>8 991 078 2848</t>
+  </si>
+  <si>
     <t>Морозова Светлана Валерьевна</t>
   </si>
   <si>
@@ -2531,6 +3011,27 @@
     <t>8 918 601 0758</t>
   </si>
   <si>
+    <t>Наливайко Валентина Герасимовна</t>
+  </si>
+  <si>
+    <t>1940-07-31</t>
+  </si>
+  <si>
+    <t>8 918 913 2372</t>
+  </si>
+  <si>
+    <t>Напылова Надежда Владимировна</t>
+  </si>
+  <si>
+    <t>Наседкина Наталья Геннадьевна</t>
+  </si>
+  <si>
+    <t>1959-04-02</t>
+  </si>
+  <si>
+    <t>8 913 686 4313</t>
+  </si>
+  <si>
     <t>Насыбуллина Равза Галимуллаевна</t>
   </si>
   <si>
@@ -2561,6 +3062,15 @@
     <t>8 928 448 3475</t>
   </si>
   <si>
+    <t>Нелюбин Владимир Ефимович</t>
+  </si>
+  <si>
+    <t>1949-01-24</t>
+  </si>
+  <si>
+    <t>8 999 656 9429</t>
+  </si>
+  <si>
     <t>Немирская Роза Гависовна</t>
   </si>
   <si>
@@ -2579,6 +3089,15 @@
     <t>8 908 677 9902</t>
   </si>
   <si>
+    <t>Нечаева Алла Александровна</t>
+  </si>
+  <si>
+    <t>1966-10-31</t>
+  </si>
+  <si>
+    <t>8 918 303 4474</t>
+  </si>
+  <si>
     <t>Никитенко Людмила Александров</t>
   </si>
   <si>
@@ -2657,12 +3176,45 @@
     <t>8 951 117 4638</t>
   </si>
   <si>
+    <t>Ноздрина Людмила Николаевна</t>
+  </si>
+  <si>
+    <t>1951-03-14</t>
+  </si>
+  <si>
+    <t>2 910 485 1366</t>
+  </si>
+  <si>
     <t>Обертайло Александр Григорьевич</t>
   </si>
   <si>
     <t>8 966 770 6515</t>
   </si>
   <si>
+    <t>Овчинникова Галина Федоровна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 918 409 0899    </t>
+  </si>
+  <si>
+    <t>Овчинникова Наталья Викторовна</t>
+  </si>
+  <si>
+    <t>1953-12-18</t>
+  </si>
+  <si>
+    <t>8 918 402 5602</t>
+  </si>
+  <si>
+    <t>Ожиганова Анастасия Николаевна</t>
+  </si>
+  <si>
+    <t>1979-02-21</t>
+  </si>
+  <si>
+    <t>8 993 326 9429</t>
+  </si>
+  <si>
     <t>Опирайло Ирина Николаевнв</t>
   </si>
   <si>
@@ -2672,15 +3224,6 @@
     <t>8 918 303 6282</t>
   </si>
   <si>
-    <t>Орел Елена Александровна</t>
-  </si>
-  <si>
-    <t>1959-03-15</t>
-  </si>
-  <si>
-    <t>8 902 912 3699</t>
-  </si>
-  <si>
     <t>Орлов Владимир Александрович</t>
   </si>
   <si>
@@ -2717,7 +3260,7 @@
     <t>8 917 207 2923</t>
   </si>
   <si>
-    <t>Охлопкова Еатерина Ивановна</t>
+    <t>Охлопкова Екатерина Ивановна</t>
   </si>
   <si>
     <t>1940-11-19</t>
@@ -2726,6 +3269,15 @@
     <t>8 913 653 2370</t>
   </si>
   <si>
+    <t>Охрименко Александр  Николаевич</t>
+  </si>
+  <si>
+    <t>1958-11-01</t>
+  </si>
+  <si>
+    <t>8 999 653 1102</t>
+  </si>
+  <si>
     <t>Павлова Вера Павловна</t>
   </si>
   <si>
@@ -2816,18 +3368,15 @@
     <t>8 928 242 9519</t>
   </si>
   <si>
-    <t>1962-02-20</t>
-  </si>
-  <si>
-    <t>2 928 242 9519</t>
-  </si>
-  <si>
-    <t>Петрова Альбина Мурнировна</t>
+    <t>Петрова Альбина Мунировна</t>
   </si>
   <si>
     <t>1960-02-04</t>
   </si>
   <si>
+    <t>8 989 958 4820</t>
+  </si>
+  <si>
     <t>Петрова Лидия Ивановна</t>
   </si>
   <si>
@@ -2870,6 +3419,15 @@
     <t>8 965 477 2915</t>
   </si>
   <si>
+    <t>Пилипенко Валентина Ивановна</t>
+  </si>
+  <si>
+    <t>1946-06-16</t>
+  </si>
+  <si>
+    <t>8 916 033 8060</t>
+  </si>
+  <si>
     <t>Пилипенко Галина Николаевна</t>
   </si>
   <si>
@@ -2879,6 +3437,15 @@
     <t>8 965 478 0130</t>
   </si>
   <si>
+    <t>Пиотровская Татьяна Анатольевна</t>
+  </si>
+  <si>
+    <t>1952-10-10</t>
+  </si>
+  <si>
+    <t>8 918 438 0507</t>
+  </si>
+  <si>
     <t>Пирогова Ирина Николаевна</t>
   </si>
   <si>
@@ -2918,12 +3485,21 @@
     <t>Полушина Неонила Исааковна</t>
   </si>
   <si>
-    <t>1940-07-12</t>
+    <t>1940-06-12</t>
   </si>
   <si>
     <t>8 938 443 9363</t>
   </si>
   <si>
+    <t>Попова Валентина Петровна</t>
+  </si>
+  <si>
+    <t>1967-03-14</t>
+  </si>
+  <si>
+    <t>8 928 448 1647</t>
+  </si>
+  <si>
     <t>Попова Татьяна Семеновна</t>
   </si>
   <si>
@@ -2948,6 +3524,15 @@
     <t>8 988 151 6260</t>
   </si>
   <si>
+    <t>Простибоженко Татьяна Николаевна</t>
+  </si>
+  <si>
+    <t>1959-09-04</t>
+  </si>
+  <si>
+    <t>8 988 411 6511</t>
+  </si>
+  <si>
     <t>Процких Валентина Владимировна</t>
   </si>
   <si>
@@ -2966,6 +3551,15 @@
     <t>8 988 142 7707</t>
   </si>
   <si>
+    <t>Пуменова Анна Геннадьевна</t>
+  </si>
+  <si>
+    <t>1964-07-26</t>
+  </si>
+  <si>
+    <t>8 913 967 0606</t>
+  </si>
+  <si>
     <t>Пустыльникова Лина Григорьевна</t>
   </si>
   <si>
@@ -3017,9 +3611,6 @@
     <t>1957-10-05</t>
   </si>
   <si>
-    <t>8 913 631 8608</t>
-  </si>
-  <si>
     <t>2 913 631 8608</t>
   </si>
   <si>
@@ -3041,6 +3632,15 @@
     <t>8 938 491 9581</t>
   </si>
   <si>
+    <t>Реднович Валерий Евстафьевич</t>
+  </si>
+  <si>
+    <t>1952-08-06</t>
+  </si>
+  <si>
+    <t>8 965 480 8255</t>
+  </si>
+  <si>
     <t>Рендович Ирина Ивановна</t>
   </si>
   <si>
@@ -3050,15 +3650,6 @@
     <t>8 909 448 0314</t>
   </si>
   <si>
-    <t>Репина Анжелла Евгеньевна</t>
-  </si>
-  <si>
-    <t>1969-08-13</t>
-  </si>
-  <si>
-    <t>8 918 919 1457</t>
-  </si>
-  <si>
     <t>Речкалова Галина Васильевна</t>
   </si>
   <si>
@@ -3077,6 +3668,9 @@
     <t>8 918 102 5976</t>
   </si>
   <si>
+    <t>Роганина Ирина Николаевна</t>
+  </si>
+  <si>
     <t>Рожкова Альфия Зинуровна</t>
   </si>
   <si>
@@ -3164,9 +3758,21 @@
     <t>Рябкова Надежда Ивановна</t>
   </si>
   <si>
+    <t>1955-03-19</t>
+  </si>
+  <si>
     <t>8 982 162 8034</t>
   </si>
   <si>
+    <t>Савоськина Людмила Сергеевна</t>
+  </si>
+  <si>
+    <t>1947-11-25</t>
+  </si>
+  <si>
+    <t>8 918 919 0016</t>
+  </si>
+  <si>
     <t>Салагаев Валерий Поликарпович</t>
   </si>
   <si>
@@ -3341,15 +3947,6 @@
     <t>8 988 189 0607</t>
   </si>
   <si>
-    <t>Сергеева Светлана Павловна</t>
-  </si>
-  <si>
-    <t>1949-06-22</t>
-  </si>
-  <si>
-    <t>8 918 202.7135</t>
-  </si>
-  <si>
     <t>Сердюк Анатолий Григорьевич</t>
   </si>
   <si>
@@ -3404,6 +4001,24 @@
     <t>8 988 169 4435</t>
   </si>
   <si>
+    <t>Ситчук Ирина Николаевна</t>
+  </si>
+  <si>
+    <t>1965-10-12</t>
+  </si>
+  <si>
+    <t>8 918 407 6741</t>
+  </si>
+  <si>
+    <t>Скворцова Альбина Васильевна</t>
+  </si>
+  <si>
+    <t>1954-11-03</t>
+  </si>
+  <si>
+    <t>2 928 666 0398</t>
+  </si>
+  <si>
     <t>Скисова Ирина Борисовна</t>
   </si>
   <si>
@@ -3431,13 +4046,13 @@
     <t>8 905 406 8699</t>
   </si>
   <si>
-    <t>Скорина Людмила Валерьевна</t>
+    <t>Скорина Людмила Валентиновна</t>
   </si>
   <si>
     <t>1949-02-24</t>
   </si>
   <si>
-    <t>8 918 145 8728</t>
+    <t>8 988 145 8728</t>
   </si>
   <si>
     <t>Скулова Ольга Ивановна</t>
@@ -3464,6 +4079,15 @@
     <t>7 918 919 0093</t>
   </si>
   <si>
+    <t>Смашнюк Елена Григорьевна</t>
+  </si>
+  <si>
+    <t>1967-09-22</t>
+  </si>
+  <si>
+    <t>8 988 531 9569</t>
+  </si>
+  <si>
     <t>Смирнова Венера Зайнуловна</t>
   </si>
   <si>
@@ -3509,6 +4133,12 @@
     <t>8 921 629 2920</t>
   </si>
   <si>
+    <t>Солдаткина Татьяна Константиновна</t>
+  </si>
+  <si>
+    <t>8 905 664 5422</t>
+  </si>
+  <si>
     <t>Соловьева Наталья Викторовна</t>
   </si>
   <si>
@@ -3548,6 +4178,24 @@
     <t>8 978 843 9370</t>
   </si>
   <si>
+    <t>Старикова Валентина Михайловна</t>
+  </si>
+  <si>
+    <t>1956-09-03</t>
+  </si>
+  <si>
+    <t>8 918 207 7863</t>
+  </si>
+  <si>
+    <t>Степанян Галина Анатольевна</t>
+  </si>
+  <si>
+    <t>1962-04-06</t>
+  </si>
+  <si>
+    <t>8 988 188 1727</t>
+  </si>
+  <si>
     <t>Степченко Светлана Владимировна</t>
   </si>
   <si>
@@ -3557,6 +4205,15 @@
     <t>8 913 147 0387</t>
   </si>
   <si>
+    <t>Стригнацкая Нафися Ивановна</t>
+  </si>
+  <si>
+    <t>1958-10-20</t>
+  </si>
+  <si>
+    <t>8 932 422 0300</t>
+  </si>
+  <si>
     <t>Струкова Инна Петровна</t>
   </si>
   <si>
@@ -3584,7 +4241,7 @@
     <t>8 916 622 0234</t>
   </si>
   <si>
-    <t>Суремкина Елена Владимировна</t>
+    <t>Суренкина Елена Владимировна</t>
   </si>
   <si>
     <t>1955-01-31</t>
@@ -3674,6 +4331,12 @@
     <t>8 988 282 4509</t>
   </si>
   <si>
+    <t>Тарасова Ольга Николаевна</t>
+  </si>
+  <si>
+    <t>1974-07-11</t>
+  </si>
+  <si>
     <t>Татаринов Владимир Данилович</t>
   </si>
   <si>
@@ -3701,6 +4364,24 @@
     <t>8 918 608 3992</t>
   </si>
   <si>
+    <t>Тимакова Наталья Анатольевна</t>
+  </si>
+  <si>
+    <t>1958-05-12</t>
+  </si>
+  <si>
+    <t>8 911 254 4084</t>
+  </si>
+  <si>
+    <t>Тихомирова Татьяна Алексеевна</t>
+  </si>
+  <si>
+    <t>1966-02-15</t>
+  </si>
+  <si>
+    <t>8 988 187 3262</t>
+  </si>
+  <si>
     <t>Тихонова Анна Леонидовна</t>
   </si>
   <si>
@@ -3743,6 +4424,15 @@
     <t>8 961 233 0097</t>
   </si>
   <si>
+    <t>Толоркова Людмила Николаевна</t>
+  </si>
+  <si>
+    <t>1947-10-01</t>
+  </si>
+  <si>
+    <t>8 902 522 7790</t>
+  </si>
+  <si>
     <t>Толстоухова Ирина Иннокентьевна</t>
   </si>
   <si>
@@ -3770,6 +4460,15 @@
     <t>8 977 021 3365</t>
   </si>
   <si>
+    <t xml:space="preserve">Тришкин Анатолий Николаевич </t>
+  </si>
+  <si>
+    <t>1949-07-29</t>
+  </si>
+  <si>
+    <t>8 918 600 4087</t>
+  </si>
+  <si>
     <t>Трофимова Елена Геннадьевна</t>
   </si>
   <si>
@@ -3788,6 +4487,15 @@
     <t>8 912 284 9646</t>
   </si>
   <si>
+    <t>Туркина Ирина Васильевна</t>
+  </si>
+  <si>
+    <t>1960-03-04</t>
+  </si>
+  <si>
+    <t>8 988 286 6169</t>
+  </si>
+  <si>
     <t>Тычинина Наталья Ивановна</t>
   </si>
   <si>
@@ -3824,6 +4532,15 @@
     <t>8 924 176 1995</t>
   </si>
   <si>
+    <t>Уткин Юрий Владимирович</t>
+  </si>
+  <si>
+    <t>1941-11-30</t>
+  </si>
+  <si>
+    <t>8 918 919 9895</t>
+  </si>
+  <si>
     <t>Уткина Наталия Вениаминовна</t>
   </si>
   <si>
@@ -3866,6 +4583,24 @@
     <t>8 918 309 4546</t>
   </si>
   <si>
+    <t>Фесенко Ольга Анатольевна</t>
+  </si>
+  <si>
+    <t>1958-08-29</t>
+  </si>
+  <si>
+    <t>8 918 329 4293</t>
+  </si>
+  <si>
+    <t>Фефилова Елена Александровна</t>
+  </si>
+  <si>
+    <t>1969-04-22</t>
+  </si>
+  <si>
+    <t>8 988 187 4600</t>
+  </si>
+  <si>
     <t>Филимонова Алла Борисовна</t>
   </si>
   <si>
@@ -3878,9 +4613,6 @@
     <t>Филиппенко Татьяна Геннадиевна</t>
   </si>
   <si>
-    <t>1957-01-22</t>
-  </si>
-  <si>
     <t>8 918 916 4343</t>
   </si>
   <si>
@@ -3893,15 +4625,6 @@
     <t>8 918 900 3223</t>
   </si>
   <si>
-    <t>Фомина Ольга Леонидовна</t>
-  </si>
-  <si>
-    <t>1963-10-17</t>
-  </si>
-  <si>
-    <t>8 918 401 5107</t>
-  </si>
-  <si>
     <t>Фоминых Раиса Петровна</t>
   </si>
   <si>
@@ -3938,6 +4661,24 @@
     <t>8 928 666 0957</t>
   </si>
   <si>
+    <t>Халиуллина Минненгуль Аглиевна</t>
+  </si>
+  <si>
+    <t>1953-03-13</t>
+  </si>
+  <si>
+    <t>8 917 254 8323</t>
+  </si>
+  <si>
+    <t>Хамидуллина Нурия Галикарамовна</t>
+  </si>
+  <si>
+    <t>1953-11-11</t>
+  </si>
+  <si>
+    <t>8 900 294 8465</t>
+  </si>
+  <si>
     <t>Харченко Любовь Васильевна</t>
   </si>
   <si>
@@ -3983,6 +4724,15 @@
     <t>8 903 700 1919</t>
   </si>
   <si>
+    <t>Храмцова Валентина Иннокентьевна</t>
+  </si>
+  <si>
+    <t>1949-01-31</t>
+  </si>
+  <si>
+    <t>8 918 601 4695</t>
+  </si>
+  <si>
     <t>Худавердиева Вера Евгеньевна</t>
   </si>
   <si>
@@ -4082,6 +4832,12 @@
     <t>8 988 142 5678</t>
   </si>
   <si>
+    <t>Черных Николай Митрофанович</t>
+  </si>
+  <si>
+    <t>1957-05-01</t>
+  </si>
+  <si>
     <t>Черных Татьяна Ивановна</t>
   </si>
   <si>
@@ -4100,7 +4856,19 @@
     <t>8 918 300 2548</t>
   </si>
   <si>
-    <t>Чернышова Людмила Борисовна</t>
+    <t>Чернявская Ольга Николаевна</t>
+  </si>
+  <si>
+    <t>1973-08-24</t>
+  </si>
+  <si>
+    <t>8 999 656 5490</t>
+  </si>
+  <si>
+    <t>Чирва Ирина Степановна</t>
+  </si>
+  <si>
+    <t>8 914 409 2213</t>
   </si>
   <si>
     <t>Чопова Лидия Андреевна</t>
@@ -4130,10 +4898,19 @@
     <t>8 918 109 3092</t>
   </si>
   <si>
-    <t>Шалагинова Вера Васильевна</t>
-  </si>
-  <si>
-    <t>8 918 305 1979</t>
+    <t>Шайхутдинов Сергей  Константинович</t>
+  </si>
+  <si>
+    <t>8 920 498 7089</t>
+  </si>
+  <si>
+    <t>Шалимова Татьяна Николаевна</t>
+  </si>
+  <si>
+    <t>1961-05-30</t>
+  </si>
+  <si>
+    <t>8 988 400 7021</t>
   </si>
   <si>
     <t>Шалыгина Валентина Владимир</t>
@@ -4163,15 +4940,6 @@
     <t>8 927 830 7189</t>
   </si>
   <si>
-    <t>Шаповалова Галина Николаевна</t>
-  </si>
-  <si>
-    <t>1948-04-20</t>
-  </si>
-  <si>
-    <t>8 967 321 6801</t>
-  </si>
-  <si>
     <t>Шарова Галина Васильевна</t>
   </si>
   <si>
@@ -4214,7 +4982,16 @@
     <t>8 983 176 9019</t>
   </si>
   <si>
-    <t>Шеховцова Марина Геннадьевна</t>
+    <t>Шеховцова Марина Николаевна</t>
+  </si>
+  <si>
+    <t>Шипоренко Ольга Викторовна</t>
+  </si>
+  <si>
+    <t>1951-07-20</t>
+  </si>
+  <si>
+    <t>8 918 401 9901</t>
   </si>
   <si>
     <t>Шкляр Светлана Николаевна</t>
@@ -4244,6 +5021,15 @@
     <t>8 902 801 7383</t>
   </si>
   <si>
+    <t>Штефанова Татьяна Александровна</t>
+  </si>
+  <si>
+    <t>1967-05-14</t>
+  </si>
+  <si>
+    <t>8 918 205 1469</t>
+  </si>
+  <si>
     <t>Шугурова Марина Владимировна</t>
   </si>
   <si>
@@ -4280,6 +5066,18 @@
     <t>8 988 151 1647</t>
   </si>
   <si>
+    <t>Шутина Ирина Валентиновна</t>
+  </si>
+  <si>
+    <t>1958-05-21</t>
+  </si>
+  <si>
+    <t>8 922 007 6612</t>
+  </si>
+  <si>
+    <t>Шутов Владимир Викентьевич</t>
+  </si>
+  <si>
     <t>Щербакова Надежда Николаевна</t>
   </si>
   <si>
@@ -4307,6 +5105,15 @@
     <t>8 928 667 8670</t>
   </si>
   <si>
+    <t>Эсмонд Аурелия</t>
+  </si>
+  <si>
+    <t>1961-01-01</t>
+  </si>
+  <si>
+    <t>8 918 607 1720</t>
+  </si>
+  <si>
     <t>Южакова Валентина Николаевна</t>
   </si>
   <si>
@@ -4343,6 +5150,9 @@
     <t>8 987 514 1077</t>
   </si>
   <si>
+    <t>Юрская Татьяна</t>
+  </si>
+  <si>
     <t>Юшков Юрий Петрович</t>
   </si>
   <si>
@@ -4359,6 +5169,15 @@
   </si>
   <si>
     <t>8 902 796 1350</t>
+  </si>
+  <si>
+    <t>Яворская Наталья Ивановнв</t>
+  </si>
+  <si>
+    <t>1953-06-18</t>
+  </si>
+  <si>
+    <t>8 918 402 4361</t>
   </si>
   <si>
     <t>Ярошенко Татьяна Анатольевна</t>
@@ -4732,7 +5551,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D503"/>
+  <dimension ref="A1:D599"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="true" style="0"/>
@@ -5099,20 +5918,22 @@
       <c r="C26" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -5120,13 +5941,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -5134,13 +5955,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -5148,14 +5969,12 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="1" t="s">
         <v>88</v>
       </c>
+      <c r="D30" s="1"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1">
@@ -5375,10 +6194,10 @@
         <v>134</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5386,13 +6205,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -5400,13 +6219,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -5414,13 +6233,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -5428,13 +6247,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -5442,13 +6261,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -5456,25 +6275,27 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D52" s="1"/>
+        <v>153</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -5482,13 +6303,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -5496,13 +6317,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -5510,13 +6331,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -5524,13 +6345,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -5538,13 +6359,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -5552,14 +6373,12 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>172</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D59" s="1"/>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1">
@@ -5597,7 +6416,7 @@
         <v>179</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>180</v>
+        <v>111</v>
       </c>
       <c r="D62" s="1"/>
     </row>
@@ -5606,13 +6425,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -5620,13 +6439,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -5634,13 +6453,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -5648,13 +6467,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -5662,13 +6481,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -5676,13 +6495,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -5690,25 +6509,27 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D69" s="1"/>
+      <c r="D69" s="1" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1">
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -5716,13 +6537,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -5730,13 +6551,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>132</v>
+        <v>208</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -5744,27 +6565,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>210</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="D73" s="1"/>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="1">
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -5772,13 +6591,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -5786,13 +6605,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -5800,13 +6619,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -5814,13 +6633,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -5828,13 +6647,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -5842,27 +6661,25 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>231</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D80" s="1"/>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="1">
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -5870,13 +6687,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -5884,27 +6701,25 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>240</v>
-      </c>
+      <c r="D83" s="1"/>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="1">
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -5912,13 +6727,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -5926,13 +6741,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -5940,13 +6755,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -5954,13 +6769,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -5968,13 +6783,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -5982,13 +6797,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -5996,13 +6811,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -6010,13 +6825,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="D92" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -6024,13 +6839,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -6038,13 +6853,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -6069,10 +6884,10 @@
         <v>275</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>34</v>
+        <v>276</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -6080,13 +6895,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -6094,13 +6909,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -6108,13 +6923,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -6122,13 +6937,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -6136,13 +6951,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -6150,13 +6965,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -6164,10 +6979,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>296</v>
+        <v>208</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>297</v>
@@ -6282,7 +7097,7 @@
         <v>320</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -6290,13 +7105,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -6304,13 +7119,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -6318,13 +7133,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -6332,13 +7147,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -6346,13 +7161,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -6360,13 +7175,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -6374,13 +7189,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -6388,13 +7203,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -6402,13 +7217,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -6416,13 +7231,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -6430,13 +7245,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="D122" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -6444,13 +7259,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -6458,13 +7273,13 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -6472,13 +7287,13 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -6486,13 +7301,13 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -6500,13 +7315,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="D127" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -6514,13 +7329,13 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="D128" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -6528,13 +7343,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="D129" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -6542,13 +7357,13 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="D130" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -6556,13 +7371,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -6570,13 +7385,13 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="D132" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -6584,13 +7399,13 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -6598,13 +7413,13 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="D134" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -6612,13 +7427,13 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="D135" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -6626,13 +7441,13 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -6640,13 +7455,13 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -6654,13 +7469,13 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -6668,13 +7483,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -6682,13 +7497,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -6696,13 +7511,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -6710,13 +7525,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -6724,13 +7539,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>132</v>
+        <v>412</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -6738,13 +7553,13 @@
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -6752,13 +7567,13 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -6766,25 +7581,27 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="D146" s="1"/>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="1">
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="D147" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -6792,13 +7609,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="D148" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -6806,13 +7623,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C149" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="D149" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -6820,13 +7637,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="D150" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -6834,13 +7651,13 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="D151" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -6848,13 +7665,13 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C152" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="D152" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -6862,13 +7679,13 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C153" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="D153" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -6876,13 +7693,13 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="D154" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -6890,13 +7707,13 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C155" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="D155" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -6904,13 +7721,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="D156" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -6918,13 +7735,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C157" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="D157" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -6932,13 +7749,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="D158" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -6946,13 +7763,13 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="D159" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -6960,13 +7777,13 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C160" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="D160" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -6974,13 +7791,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="D161" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -6988,13 +7805,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="D162" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -7002,13 +7819,13 @@
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="D163" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -7016,13 +7833,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="D164" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -7030,25 +7847,27 @@
         <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D165" s="1"/>
+      <c r="D165" s="1" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="1">
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -7056,13 +7875,13 @@
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -7070,13 +7889,13 @@
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -7084,13 +7903,13 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -7098,10 +7917,10 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>492</v>
+        <v>111</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>493</v>
@@ -7159,22 +7978,20 @@
       <c r="C174" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="D174" s="1" t="s">
-        <v>505</v>
-      </c>
+      <c r="D174" s="1"/>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="1">
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C175" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="C175" s="1" t="s">
+      <c r="D175" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -7182,13 +7999,13 @@
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C176" s="1" t="s">
+      <c r="D176" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -7196,13 +8013,13 @@
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C177" s="1" t="s">
+      <c r="D177" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -7210,13 +8027,13 @@
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C178" s="1" t="s">
+      <c r="D178" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -7224,13 +8041,13 @@
         <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C179" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="C179" s="1" t="s">
+      <c r="D179" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -7238,13 +8055,13 @@
         <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C180" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C180" s="1" t="s">
+      <c r="D180" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -7252,10 +8069,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C181" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>525</v>
@@ -7451,23 +8268,23 @@
         <v>565</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>567</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D195" s="1"/>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="1">
         <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D196" s="1"/>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="1">
@@ -7619,20 +8436,22 @@
       <c r="C207" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="D207" s="1"/>
+      <c r="D207" s="1" t="s">
+        <v>601</v>
+      </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="1">
         <v>207</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -7640,13 +8459,13 @@
         <v>208</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -7654,13 +8473,13 @@
         <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -7668,10 +8487,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>611</v>
+        <v>276</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>612</v>
@@ -7909,38 +8728,34 @@
         <v>661</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>663</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D228" s="1"/>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="1">
         <v>228</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>666</v>
-      </c>
+        <v>663</v>
+      </c>
+      <c r="D229" s="1"/>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="1">
         <v>229</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -7948,13 +8763,13 @@
         <v>230</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -7962,13 +8777,13 @@
         <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -7976,13 +8791,13 @@
         <v>232</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -7990,41 +8805,37 @@
         <v>233</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>681</v>
-      </c>
+        <v>677</v>
+      </c>
+      <c r="D234" s="1"/>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="1">
         <v>234</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>684</v>
-      </c>
+        <v>679</v>
+      </c>
+      <c r="D235" s="1"/>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="1">
         <v>235</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -8032,13 +8843,13 @@
         <v>236</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -8046,13 +8857,13 @@
         <v>237</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -8060,13 +8871,13 @@
         <v>238</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -8074,13 +8885,13 @@
         <v>239</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -8088,13 +8899,13 @@
         <v>240</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -8102,13 +8913,13 @@
         <v>241</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -8116,27 +8927,25 @@
         <v>242</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>708</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="D243" s="1"/>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="1">
         <v>243</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -8144,25 +8953,27 @@
         <v>244</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="D245" s="1"/>
+        <v>707</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>708</v>
+      </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="1">
         <v>245</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>132</v>
+        <v>710</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -8170,13 +8981,13 @@
         <v>246</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>132</v>
+        <v>713</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -8184,13 +8995,13 @@
         <v>247</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -8198,13 +9009,13 @@
         <v>248</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -8212,13 +9023,13 @@
         <v>249</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -8226,13 +9037,13 @@
         <v>250</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -8240,13 +9051,13 @@
         <v>251</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -8254,13 +9065,13 @@
         <v>252</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -8268,13 +9079,13 @@
         <v>253</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -8282,13 +9093,13 @@
         <v>254</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -8296,13 +9107,13 @@
         <v>255</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -8310,13 +9121,13 @@
         <v>256</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>746</v>
+        <v>294</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -8324,13 +9135,13 @@
         <v>257</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -8338,13 +9149,13 @@
         <v>258</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -8352,13 +9163,13 @@
         <v>259</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -8366,13 +9177,13 @@
         <v>260</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -8380,13 +9191,13 @@
         <v>261</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -8394,13 +9205,13 @@
         <v>262</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>273</v>
+        <v>759</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -8408,13 +9219,13 @@
         <v>263</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -8422,13 +9233,13 @@
         <v>264</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -8436,13 +9247,13 @@
         <v>265</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -8450,13 +9261,13 @@
         <v>266</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -8464,13 +9275,13 @@
         <v>267</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -8478,13 +9289,13 @@
         <v>268</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -8492,13 +9303,13 @@
         <v>269</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -8506,13 +9317,13 @@
         <v>270</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -8520,13 +9331,13 @@
         <v>271</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -8534,13 +9345,13 @@
         <v>272</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -8548,13 +9359,13 @@
         <v>273</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -8562,13 +9373,13 @@
         <v>274</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -8576,13 +9387,13 @@
         <v>275</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -8590,13 +9401,13 @@
         <v>276</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -8604,13 +9415,13 @@
         <v>277</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -8618,13 +9429,13 @@
         <v>278</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -8632,13 +9443,13 @@
         <v>279</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>25</v>
+        <v>810</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -8646,13 +9457,13 @@
         <v>280</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -8660,13 +9471,13 @@
         <v>281</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -8674,13 +9485,13 @@
         <v>282</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -8688,13 +9499,13 @@
         <v>283</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -8702,27 +9513,25 @@
         <v>284</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>829</v>
-      </c>
+        <v>825</v>
+      </c>
+      <c r="D285" s="1"/>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="1">
         <v>285</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -8730,13 +9539,13 @@
         <v>286</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>437</v>
+        <v>830</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -8744,13 +9553,13 @@
         <v>287</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -8758,13 +9567,13 @@
         <v>288</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -8772,13 +9581,13 @@
         <v>289</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -8786,25 +9595,27 @@
         <v>290</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D291" s="1"/>
+        <v>842</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" s="1">
         <v>291</v>
       </c>
       <c r="B292" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="C292" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="C292" s="1" t="s">
+      <c r="D292" s="1" t="s">
         <v>846</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -8812,27 +9623,25 @@
         <v>292</v>
       </c>
       <c r="B293" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="C293" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="C293" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>850</v>
-      </c>
+      <c r="D293" s="1"/>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" s="1">
         <v>293</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>852</v>
+        <v>111</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -8840,13 +9649,13 @@
         <v>294</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -8854,13 +9663,13 @@
         <v>295</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -8868,13 +9677,13 @@
         <v>296</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -8882,13 +9691,13 @@
         <v>297</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -8896,13 +9705,13 @@
         <v>298</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>867</v>
+        <v>836</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -8910,13 +9719,13 @@
         <v>299</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>725</v>
+        <v>866</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -8924,13 +9733,13 @@
         <v>300</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -8938,13 +9747,13 @@
         <v>301</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -8952,13 +9761,13 @@
         <v>302</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -8966,13 +9775,13 @@
         <v>303</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>614</v>
+        <v>878</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -8980,13 +9789,13 @@
         <v>304</v>
       </c>
       <c r="B305" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="D305" s="1" t="s">
         <v>882</v>
-      </c>
-      <c r="C305" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -8994,13 +9803,13 @@
         <v>305</v>
       </c>
       <c r="B306" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="D306" s="1" t="s">
         <v>885</v>
-      </c>
-      <c r="C306" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -9008,13 +9817,13 @@
         <v>306</v>
       </c>
       <c r="B307" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>888</v>
-      </c>
-      <c r="C307" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -9022,13 +9831,13 @@
         <v>307</v>
       </c>
       <c r="B308" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="D308" s="1" t="s">
         <v>891</v>
-      </c>
-      <c r="C308" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -9036,13 +9845,13 @@
         <v>308</v>
       </c>
       <c r="B309" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="D309" s="1" t="s">
         <v>894</v>
-      </c>
-      <c r="C309" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -9050,13 +9859,13 @@
         <v>309</v>
       </c>
       <c r="B310" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="D310" s="1" t="s">
         <v>897</v>
-      </c>
-      <c r="C310" s="1" t="s">
-        <v>898</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -9064,13 +9873,13 @@
         <v>310</v>
       </c>
       <c r="B311" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>900</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -9078,13 +9887,13 @@
         <v>311</v>
       </c>
       <c r="B312" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="D312" s="1" t="s">
         <v>903</v>
-      </c>
-      <c r="C312" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -9092,13 +9901,13 @@
         <v>312</v>
       </c>
       <c r="B313" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>906</v>
-      </c>
-      <c r="C313" s="1" t="s">
-        <v>907</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -9106,13 +9915,13 @@
         <v>313</v>
       </c>
       <c r="B314" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="D314" s="1" t="s">
         <v>909</v>
-      </c>
-      <c r="C314" s="1" t="s">
-        <v>910</v>
-      </c>
-      <c r="D314" s="1" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -9120,13 +9929,13 @@
         <v>314</v>
       </c>
       <c r="B315" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="D315" s="1" t="s">
         <v>912</v>
-      </c>
-      <c r="C315" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="D315" s="1" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -9134,13 +9943,13 @@
         <v>315</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -9148,13 +9957,13 @@
         <v>316</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -9162,10 +9971,10 @@
         <v>317</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>919</v>
+        <v>325</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>920</v>
@@ -9232,13 +10041,13 @@
         <v>322</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -9246,25 +10055,27 @@
         <v>323</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>936</v>
-      </c>
-      <c r="D324" s="1"/>
+        <v>937</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>938</v>
+      </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" s="1">
         <v>324</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -9272,13 +10083,13 @@
         <v>325</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -9286,13 +10097,13 @@
         <v>326</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>858</v>
+        <v>946</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -9300,13 +10111,13 @@
         <v>327</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -9314,13 +10125,13 @@
         <v>328</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -9328,27 +10139,25 @@
         <v>329</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>952</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>953</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D330" s="1"/>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" s="1">
         <v>330</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -9356,13 +10165,13 @@
         <v>331</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -9370,13 +10179,13 @@
         <v>332</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -9384,13 +10193,13 @@
         <v>333</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -9398,13 +10207,13 @@
         <v>334</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -9412,10 +10221,10 @@
         <v>335</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>971</v>
@@ -9443,10 +10252,10 @@
         <v>975</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>931</v>
+        <v>976</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -9454,13 +10263,13 @@
         <v>338</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -9468,13 +10277,13 @@
         <v>339</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -9482,13 +10291,13 @@
         <v>340</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -9496,13 +10305,13 @@
         <v>341</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -9510,13 +10319,13 @@
         <v>342</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -9524,10 +10333,10 @@
         <v>343</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>993</v>
+        <v>521</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>994</v>
@@ -9566,14 +10375,12 @@
         <v>346</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>999</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>1001</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D347" s="1"/>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" s="1">
@@ -9625,24 +10432,22 @@
         <v>1011</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>1013</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D351" s="1"/>
     </row>
     <row r="352" spans="1:4">
       <c r="A352" s="1">
         <v>351</v>
       </c>
       <c r="B352" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D352" s="1" t="s">
         <v>1014</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -9650,13 +10455,13 @@
         <v>352</v>
       </c>
       <c r="B353" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D353" s="1" t="s">
         <v>1017</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -9664,13 +10469,13 @@
         <v>353</v>
       </c>
       <c r="B354" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D354" s="1" t="s">
         <v>1020</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -9678,13 +10483,13 @@
         <v>354</v>
       </c>
       <c r="B355" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D355" s="1" t="s">
         <v>1023</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -9692,13 +10497,13 @@
         <v>355</v>
       </c>
       <c r="B356" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D356" s="1" t="s">
         <v>1026</v>
-      </c>
-      <c r="C356" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D356" s="1" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -9706,13 +10511,13 @@
         <v>356</v>
       </c>
       <c r="B357" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D357" s="1" t="s">
         <v>1029</v>
-      </c>
-      <c r="C357" s="1" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D357" s="1" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -9720,13 +10525,13 @@
         <v>357</v>
       </c>
       <c r="B358" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D358" s="1" t="s">
         <v>1032</v>
-      </c>
-      <c r="C358" s="1" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D358" s="1" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -9734,13 +10539,13 @@
         <v>358</v>
       </c>
       <c r="B359" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D359" s="1" t="s">
         <v>1035</v>
-      </c>
-      <c r="C359" s="1" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D359" s="1" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -9748,13 +10553,13 @@
         <v>359</v>
       </c>
       <c r="B360" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D360" s="1" t="s">
         <v>1038</v>
-      </c>
-      <c r="C360" s="1" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D360" s="1" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -9762,13 +10567,13 @@
         <v>360</v>
       </c>
       <c r="B361" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D361" s="1" t="s">
         <v>1041</v>
-      </c>
-      <c r="C361" s="1" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D361" s="1" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -9776,13 +10581,13 @@
         <v>361</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>1021</v>
+        <v>869</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>1022</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -9790,13 +10595,13 @@
         <v>362</v>
       </c>
       <c r="B363" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C363" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="C363" s="1" t="s">
+      <c r="D363" s="1" t="s">
         <v>1046</v>
-      </c>
-      <c r="D363" s="1" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -9804,10 +10609,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C364" s="1" t="s">
         <v>1048</v>
-      </c>
-      <c r="C364" s="1" t="s">
-        <v>573</v>
       </c>
       <c r="D364" s="1" t="s">
         <v>1049</v>
@@ -9849,10 +10654,10 @@
         <v>1056</v>
       </c>
       <c r="C367" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="D367" s="1" t="s">
         <v>1057</v>
-      </c>
-      <c r="D367" s="1" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -9860,13 +10665,13 @@
         <v>367</v>
       </c>
       <c r="B368" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D368" s="1" t="s">
         <v>1059</v>
-      </c>
-      <c r="C368" s="1" t="s">
-        <v>1060</v>
-      </c>
-      <c r="D368" s="1" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -9874,13 +10679,13 @@
         <v>368</v>
       </c>
       <c r="B369" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D369" s="1" t="s">
         <v>1062</v>
-      </c>
-      <c r="C369" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D369" s="1" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -9888,13 +10693,13 @@
         <v>369</v>
       </c>
       <c r="B370" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D370" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="C370" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D370" s="1" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -9902,13 +10707,13 @@
         <v>370</v>
       </c>
       <c r="B371" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D371" s="1" t="s">
         <v>1068</v>
-      </c>
-      <c r="C371" s="1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D371" s="1" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -9916,13 +10721,13 @@
         <v>371</v>
       </c>
       <c r="B372" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D372" s="1" t="s">
         <v>1071</v>
-      </c>
-      <c r="C372" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="D372" s="1" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -9930,13 +10735,13 @@
         <v>372</v>
       </c>
       <c r="B373" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C373" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="C373" s="1" t="s">
+      <c r="D373" s="1" t="s">
         <v>1074</v>
-      </c>
-      <c r="D373" s="1" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -9944,13 +10749,13 @@
         <v>373</v>
       </c>
       <c r="B374" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C374" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="C374" s="1" t="s">
+      <c r="D374" s="1" t="s">
         <v>1077</v>
-      </c>
-      <c r="D374" s="1">
-        <v>89181060053</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -10185,10 +10990,10 @@
         <v>1126</v>
       </c>
       <c r="C391" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D391" s="1" t="s">
         <v>1127</v>
-      </c>
-      <c r="D391" s="1" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -10196,13 +11001,13 @@
         <v>391</v>
       </c>
       <c r="B392" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C392" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="C392" s="1" t="s">
+      <c r="D392" s="1" t="s">
         <v>1130</v>
-      </c>
-      <c r="D392" s="1" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -10210,13 +11015,13 @@
         <v>392</v>
       </c>
       <c r="B393" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C393" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="C393" s="1" t="s">
+      <c r="D393" s="1" t="s">
         <v>1133</v>
-      </c>
-      <c r="D393" s="1" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -10224,13 +11029,13 @@
         <v>393</v>
       </c>
       <c r="B394" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C394" s="1" t="s">
         <v>1135</v>
       </c>
-      <c r="C394" s="1" t="s">
+      <c r="D394" s="1" t="s">
         <v>1136</v>
-      </c>
-      <c r="D394" s="1" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -10238,13 +11043,13 @@
         <v>394</v>
       </c>
       <c r="B395" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C395" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="C395" s="1" t="s">
+      <c r="D395" s="1" t="s">
         <v>1139</v>
-      </c>
-      <c r="D395" s="1" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -10252,10 +11057,10 @@
         <v>395</v>
       </c>
       <c r="B396" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C396" s="1" t="s">
         <v>1141</v>
-      </c>
-      <c r="C396" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="D396" s="1" t="s">
         <v>1142</v>
@@ -10381,7 +11186,7 @@
         <v>1167</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>132</v>
+        <v>1115</v>
       </c>
       <c r="D405" s="1" t="s">
         <v>1168</v>
@@ -10409,10 +11214,10 @@
         <v>1172</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>11</v>
+        <v>1173</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -10420,13 +11225,13 @@
         <v>407</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -10434,13 +11239,13 @@
         <v>408</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -10448,13 +11253,13 @@
         <v>409</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -10462,13 +11267,13 @@
         <v>410</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -10476,13 +11281,13 @@
         <v>411</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -10490,13 +11295,13 @@
         <v>412</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -10504,13 +11309,13 @@
         <v>413</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -10518,13 +11323,13 @@
         <v>414</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -10532,13 +11337,13 @@
         <v>415</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -10546,13 +11351,13 @@
         <v>416</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -10560,13 +11365,13 @@
         <v>417</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -10574,13 +11379,13 @@
         <v>418</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -10588,13 +11393,13 @@
         <v>419</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -10602,13 +11407,13 @@
         <v>420</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -10616,13 +11421,13 @@
         <v>421</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>1217</v>
+        <v>789</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>1218</v>
+        <v>790</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -10630,13 +11435,13 @@
         <v>422</v>
       </c>
       <c r="B423" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C423" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="C423" s="1" t="s">
+      <c r="D423" s="1" t="s">
         <v>1220</v>
-      </c>
-      <c r="D423" s="1" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -10644,13 +11449,13 @@
         <v>423</v>
       </c>
       <c r="B424" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C424" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="C424" s="1" t="s">
+      <c r="D424" s="1" t="s">
         <v>1223</v>
-      </c>
-      <c r="D424" s="1" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -10658,13 +11463,13 @@
         <v>424</v>
       </c>
       <c r="B425" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C425" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="C425" s="1" t="s">
+      <c r="D425" s="1" t="s">
         <v>1226</v>
-      </c>
-      <c r="D425" s="1" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -10672,13 +11477,13 @@
         <v>425</v>
       </c>
       <c r="B426" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C426" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="C426" s="1" t="s">
+      <c r="D426" s="1" t="s">
         <v>1229</v>
-      </c>
-      <c r="D426" s="1" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -10686,13 +11491,13 @@
         <v>426</v>
       </c>
       <c r="B427" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C427" s="1" t="s">
         <v>1231</v>
       </c>
-      <c r="C427" s="1" t="s">
+      <c r="D427" s="1" t="s">
         <v>1232</v>
-      </c>
-      <c r="D427" s="1" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -10700,13 +11505,13 @@
         <v>427</v>
       </c>
       <c r="B428" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C428" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="C428" s="1" t="s">
+      <c r="D428" s="1" t="s">
         <v>1235</v>
-      </c>
-      <c r="D428" s="1" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -10714,13 +11519,13 @@
         <v>428</v>
       </c>
       <c r="B429" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C429" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="C429" s="1" t="s">
+      <c r="D429" s="1" t="s">
         <v>1238</v>
-      </c>
-      <c r="D429" s="1" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -10728,7 +11533,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>1240</v>
@@ -10745,10 +11550,10 @@
         <v>1242</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>1243</v>
+        <v>1219</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>1244</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -10756,13 +11561,13 @@
         <v>431</v>
       </c>
       <c r="B432" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C432" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D432" s="1" t="s">
         <v>1245</v>
-      </c>
-      <c r="C432" s="1" t="s">
-        <v>1246</v>
-      </c>
-      <c r="D432" s="1" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -10770,13 +11575,13 @@
         <v>432</v>
       </c>
       <c r="B433" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C433" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D433" s="1" t="s">
         <v>1248</v>
-      </c>
-      <c r="C433" s="1" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D433" s="1" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -10784,13 +11589,13 @@
         <v>433</v>
       </c>
       <c r="B434" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D434" s="1" t="s">
         <v>1251</v>
-      </c>
-      <c r="C434" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="D434" s="1" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -10798,13 +11603,13 @@
         <v>434</v>
       </c>
       <c r="B435" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D435" s="1" t="s">
         <v>1254</v>
-      </c>
-      <c r="C435" s="1" t="s">
-        <v>1255</v>
-      </c>
-      <c r="D435" s="1" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -10812,13 +11617,13 @@
         <v>435</v>
       </c>
       <c r="B436" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D436" s="1" t="s">
         <v>1257</v>
-      </c>
-      <c r="C436" s="1" t="s">
-        <v>1258</v>
-      </c>
-      <c r="D436" s="1" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -10826,13 +11631,13 @@
         <v>436</v>
       </c>
       <c r="B437" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C437" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D437" s="1" t="s">
         <v>1260</v>
-      </c>
-      <c r="C437" s="1" t="s">
-        <v>1261</v>
-      </c>
-      <c r="D437" s="1" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -10840,13 +11645,13 @@
         <v>437</v>
       </c>
       <c r="B438" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C438" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D438" s="1" t="s">
         <v>1263</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>1264</v>
-      </c>
-      <c r="D438" s="1" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -10854,13 +11659,13 @@
         <v>438</v>
       </c>
       <c r="B439" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D439" s="1" t="s">
         <v>1266</v>
-      </c>
-      <c r="C439" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="D439" s="1" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -10868,13 +11673,13 @@
         <v>439</v>
       </c>
       <c r="B440" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C440" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D440" s="1" t="s">
         <v>1269</v>
-      </c>
-      <c r="C440" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="D440" s="1" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -10882,13 +11687,13 @@
         <v>440</v>
       </c>
       <c r="B441" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C441" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D441" s="1" t="s">
         <v>1272</v>
-      </c>
-      <c r="C441" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="D441" s="1" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -10896,13 +11701,13 @@
         <v>441</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>495</v>
+        <v>551</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -10910,13 +11715,13 @@
         <v>442</v>
       </c>
       <c r="B443" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C443" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D443" s="1" t="s">
         <v>1277</v>
-      </c>
-      <c r="C443" s="1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="D443" s="1" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -10924,13 +11729,13 @@
         <v>443</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D444" s="1" t="s">
-        <v>1282</v>
+        <v>1279</v>
+      </c>
+      <c r="D444" s="1">
+        <v>89181060053</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -10938,13 +11743,13 @@
         <v>444</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -10952,13 +11757,13 @@
         <v>445</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -10966,13 +11771,13 @@
         <v>446</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -10980,13 +11785,13 @@
         <v>447</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -10994,13 +11799,13 @@
         <v>448</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -11008,13 +11813,13 @@
         <v>449</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -11022,13 +11827,13 @@
         <v>450</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -11036,13 +11841,13 @@
         <v>451</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -11050,13 +11855,13 @@
         <v>452</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -11064,13 +11869,13 @@
         <v>453</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -11078,13 +11883,13 @@
         <v>454</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -11092,13 +11897,13 @@
         <v>455</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -11106,13 +11911,13 @@
         <v>456</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -11120,13 +11925,13 @@
         <v>457</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -11134,13 +11939,13 @@
         <v>458</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -11148,13 +11953,13 @@
         <v>459</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -11162,13 +11967,13 @@
         <v>460</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -11176,13 +11981,13 @@
         <v>461</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -11190,13 +11995,13 @@
         <v>462</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -11204,13 +12009,13 @@
         <v>463</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -11218,13 +12023,13 @@
         <v>464</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -11232,13 +12037,13 @@
         <v>465</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -11246,13 +12051,13 @@
         <v>466</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>1350</v>
+        <v>905</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -11260,13 +12065,13 @@
         <v>467</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -11274,13 +12079,13 @@
         <v>468</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -11288,13 +12093,13 @@
         <v>469</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -11302,25 +12107,27 @@
         <v>470</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D471" s="1"/>
+        <v>1358</v>
+      </c>
+      <c r="D471" s="1" t="s">
+        <v>1359</v>
+      </c>
     </row>
     <row r="472" spans="1:4">
       <c r="A472" s="1">
         <v>471</v>
       </c>
       <c r="B472" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C472" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D472" s="1" t="s">
         <v>1362</v>
-      </c>
-      <c r="C472" s="1" t="s">
-        <v>1363</v>
-      </c>
-      <c r="D472" s="1" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -11328,13 +12135,13 @@
         <v>472</v>
       </c>
       <c r="B473" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C473" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D473" s="1" t="s">
         <v>1365</v>
-      </c>
-      <c r="C473" s="1" t="s">
-        <v>1366</v>
-      </c>
-      <c r="D473" s="1" t="s">
-        <v>1367</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -11342,13 +12149,13 @@
         <v>473</v>
       </c>
       <c r="B474" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C474" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D474" s="1" t="s">
         <v>1368</v>
-      </c>
-      <c r="C474" s="1" t="s">
-        <v>1369</v>
-      </c>
-      <c r="D474" s="1" t="s">
-        <v>1370</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -11356,13 +12163,13 @@
         <v>474</v>
       </c>
       <c r="B475" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D475" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C475" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D475" s="1" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -11370,13 +12177,13 @@
         <v>475</v>
       </c>
       <c r="B476" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C476" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D476" s="1" t="s">
         <v>1373</v>
-      </c>
-      <c r="C476" s="1" t="s">
-        <v>1374</v>
-      </c>
-      <c r="D476" s="1" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -11384,13 +12191,13 @@
         <v>476</v>
       </c>
       <c r="B477" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D477" s="1" t="s">
         <v>1376</v>
-      </c>
-      <c r="C477" s="1" t="s">
-        <v>1377</v>
-      </c>
-      <c r="D477" s="1" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -11398,13 +12205,13 @@
         <v>477</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>1380</v>
+        <v>111</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -11412,13 +12219,13 @@
         <v>478</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -11426,13 +12233,13 @@
         <v>479</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>1386</v>
+        <v>11</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -11440,13 +12247,13 @@
         <v>480</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>425</v>
+        <v>1385</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -11454,13 +12261,13 @@
         <v>481</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -11468,13 +12275,13 @@
         <v>482</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -11482,13 +12289,13 @@
         <v>483</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -11496,25 +12303,27 @@
         <v>484</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D485" s="1"/>
+        <v>1397</v>
+      </c>
+      <c r="D485" s="1" t="s">
+        <v>1398</v>
+      </c>
     </row>
     <row r="486" spans="1:4">
       <c r="A486" s="1">
         <v>485</v>
       </c>
       <c r="B486" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C486" s="1" t="s">
         <v>1400</v>
       </c>
-      <c r="C486" s="1" t="s">
+      <c r="D486" s="1" t="s">
         <v>1401</v>
-      </c>
-      <c r="D486" s="1" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -11522,13 +12331,13 @@
         <v>486</v>
       </c>
       <c r="B487" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C487" s="1" t="s">
         <v>1403</v>
       </c>
-      <c r="C487" s="1" t="s">
+      <c r="D487" s="1" t="s">
         <v>1404</v>
-      </c>
-      <c r="D487" s="1" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -11536,13 +12345,13 @@
         <v>487</v>
       </c>
       <c r="B488" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C488" s="1" t="s">
         <v>1406</v>
       </c>
-      <c r="C488" s="1" t="s">
+      <c r="D488" s="1" t="s">
         <v>1407</v>
-      </c>
-      <c r="D488" s="1" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -11550,13 +12359,13 @@
         <v>488</v>
       </c>
       <c r="B489" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C489" s="1" t="s">
         <v>1409</v>
       </c>
-      <c r="C489" s="1" t="s">
+      <c r="D489" s="1" t="s">
         <v>1410</v>
-      </c>
-      <c r="D489" s="1" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -11564,13 +12373,13 @@
         <v>489</v>
       </c>
       <c r="B490" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C490" s="1" t="s">
         <v>1412</v>
       </c>
-      <c r="C490" s="1" t="s">
+      <c r="D490" s="1" t="s">
         <v>1413</v>
-      </c>
-      <c r="D490" s="1" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -11578,13 +12387,13 @@
         <v>490</v>
       </c>
       <c r="B491" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C491" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="C491" s="1" t="s">
+      <c r="D491" s="1" t="s">
         <v>1416</v>
-      </c>
-      <c r="D491" s="1" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -11592,13 +12401,13 @@
         <v>491</v>
       </c>
       <c r="B492" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C492" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="C492" s="1" t="s">
+      <c r="D492" s="1" t="s">
         <v>1419</v>
-      </c>
-      <c r="D492" s="1" t="s">
-        <v>1420</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -11606,13 +12415,13 @@
         <v>492</v>
       </c>
       <c r="B493" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C493" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="C493" s="1" t="s">
+      <c r="D493" s="1" t="s">
         <v>1422</v>
-      </c>
-      <c r="D493" s="1" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -11620,13 +12429,13 @@
         <v>493</v>
       </c>
       <c r="B494" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C494" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="C494" s="1" t="s">
+      <c r="D494" s="1" t="s">
         <v>1425</v>
-      </c>
-      <c r="D494" s="1" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -11634,13 +12443,13 @@
         <v>494</v>
       </c>
       <c r="B495" s="1" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C495" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="C495" s="1" t="s">
+      <c r="D495" s="1" t="s">
         <v>1428</v>
-      </c>
-      <c r="D495" s="1" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -11648,13 +12457,13 @@
         <v>495</v>
       </c>
       <c r="B496" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C496" s="1" t="s">
         <v>1430</v>
       </c>
-      <c r="C496" s="1" t="s">
+      <c r="D496" s="1" t="s">
         <v>1431</v>
-      </c>
-      <c r="D496" s="1" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -11662,13 +12471,13 @@
         <v>496</v>
       </c>
       <c r="B497" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C497" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="C497" s="1" t="s">
+      <c r="D497" s="1" t="s">
         <v>1434</v>
-      </c>
-      <c r="D497" s="1" t="s">
-        <v>1435</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -11676,13 +12485,13 @@
         <v>497</v>
       </c>
       <c r="B498" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C498" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="C498" s="1" t="s">
+      <c r="D498" s="1" t="s">
         <v>1437</v>
-      </c>
-      <c r="D498" s="1" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -11690,27 +12499,25 @@
         <v>498</v>
       </c>
       <c r="B499" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C499" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="C499" s="1" t="s">
-        <v>1440</v>
-      </c>
-      <c r="D499" s="1" t="s">
-        <v>1441</v>
-      </c>
+      <c r="D499" s="1"/>
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
         <v>499</v>
       </c>
       <c r="B500" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C500" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D500" s="1" t="s">
         <v>1442</v>
-      </c>
-      <c r="C500" s="1" t="s">
-        <v>1443</v>
-      </c>
-      <c r="D500" s="1" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -11718,13 +12525,13 @@
         <v>500</v>
       </c>
       <c r="B501" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C501" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D501" s="1" t="s">
         <v>1445</v>
-      </c>
-      <c r="C501" s="1" t="s">
-        <v>1446</v>
-      </c>
-      <c r="D501" s="1" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -11732,13 +12539,13 @@
         <v>501</v>
       </c>
       <c r="B502" s="1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C502" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D502" s="1" t="s">
         <v>1448</v>
-      </c>
-      <c r="C502" s="1" t="s">
-        <v>1449</v>
-      </c>
-      <c r="D502" s="1" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -11746,13 +12553,1349 @@
         <v>502</v>
       </c>
       <c r="B503" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C503" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D503" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="C503" s="1" t="s">
+    </row>
+    <row r="504" spans="1:4">
+      <c r="A504" s="1">
+        <v>503</v>
+      </c>
+      <c r="B504" s="1" t="s">
         <v>1452</v>
       </c>
-      <c r="D503" s="1" t="s">
+      <c r="C504" s="1" t="s">
         <v>1453</v>
+      </c>
+      <c r="D504" s="1" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4">
+      <c r="A505" s="1">
+        <v>504</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C505" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D505" s="1" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4">
+      <c r="A506" s="1">
+        <v>505</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C506" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D506" s="1" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4">
+      <c r="A507" s="1">
+        <v>506</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C507" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D507" s="1" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4">
+      <c r="A508" s="1">
+        <v>507</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C508" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D508" s="1" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4">
+      <c r="A509" s="1">
+        <v>508</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C509" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D509" s="1" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4">
+      <c r="A510" s="1">
+        <v>509</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C510" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D510" s="1" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4">
+      <c r="A511" s="1">
+        <v>510</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C511" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D511" s="1" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4">
+      <c r="A512" s="1">
+        <v>511</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C512" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D512" s="1" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4">
+      <c r="A513" s="1">
+        <v>512</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D513" s="1" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4">
+      <c r="A514" s="1">
+        <v>513</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C514" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D514" s="1" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4">
+      <c r="A515" s="1">
+        <v>514</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C515" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D515" s="1" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4">
+      <c r="A516" s="1">
+        <v>515</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C516" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D516" s="1" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4">
+      <c r="A517" s="1">
+        <v>516</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D517" s="1" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4">
+      <c r="A518" s="1">
+        <v>517</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C518" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D518" s="1" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4">
+      <c r="A519" s="1">
+        <v>518</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C519" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D519" s="1" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4">
+      <c r="A520" s="1">
+        <v>519</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C520" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D520" s="1" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4">
+      <c r="A521" s="1">
+        <v>520</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C521" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D521" s="1" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4">
+      <c r="A522" s="1">
+        <v>521</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C522" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D522" s="1" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4">
+      <c r="A523" s="1">
+        <v>522</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D523" s="1" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4">
+      <c r="A524" s="1">
+        <v>523</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C524" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D524" s="1" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4">
+      <c r="A525" s="1">
+        <v>524</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C525" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D525" s="1" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4">
+      <c r="A526" s="1">
+        <v>525</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C526" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D526" s="1" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4">
+      <c r="A527" s="1">
+        <v>526</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C527" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D527" s="1" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4">
+      <c r="A528" s="1">
+        <v>527</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D528" s="1" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4">
+      <c r="A529" s="1">
+        <v>528</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C529" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D529" s="1" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4">
+      <c r="A530" s="1">
+        <v>529</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C530" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D530" s="1" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4">
+      <c r="A531" s="1">
+        <v>530</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C531" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D531" s="1" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4">
+      <c r="A532" s="1">
+        <v>531</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C532" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D532" s="1" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4">
+      <c r="A533" s="1">
+        <v>532</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C533" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D533" s="1" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4">
+      <c r="A534" s="1">
+        <v>533</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C534" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D534" s="1" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4">
+      <c r="A535" s="1">
+        <v>534</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C535" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D535" s="1" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4">
+      <c r="A536" s="1">
+        <v>535</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C536" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D536" s="1" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4">
+      <c r="A537" s="1">
+        <v>536</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C537" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D537" s="1" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4">
+      <c r="A538" s="1">
+        <v>537</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C538" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D538" s="1" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4">
+      <c r="A539" s="1">
+        <v>538</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C539" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D539" s="1" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4">
+      <c r="A540" s="1">
+        <v>539</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D540" s="1" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4">
+      <c r="A541" s="1">
+        <v>540</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C541" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D541" s="1" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4">
+      <c r="A542" s="1">
+        <v>541</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C542" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D542" s="1" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4">
+      <c r="A543" s="1">
+        <v>542</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C543" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D543" s="1" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4">
+      <c r="A544" s="1">
+        <v>543</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C544" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D544" s="1" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4">
+      <c r="A545" s="1">
+        <v>544</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C545" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D545" s="1" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4">
+      <c r="A546" s="1">
+        <v>545</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C546" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D546" s="1" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4">
+      <c r="A547" s="1">
+        <v>546</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C547" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D547" s="1" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4">
+      <c r="A548" s="1">
+        <v>547</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C548" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D548" s="1" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4">
+      <c r="A549" s="1">
+        <v>548</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C549" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D549" s="1" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4">
+      <c r="A550" s="1">
+        <v>549</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C550" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D550" s="1" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4">
+      <c r="A551" s="1">
+        <v>550</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C551" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D551" s="1" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4">
+      <c r="A552" s="1">
+        <v>551</v>
+      </c>
+      <c r="B552" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C552" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D552" s="1" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4">
+      <c r="A553" s="1">
+        <v>552</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C553" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D553" s="1" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4">
+      <c r="A554" s="1">
+        <v>553</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C554" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D554" s="1" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4">
+      <c r="A555" s="1">
+        <v>554</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C555" s="1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D555" s="1" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4">
+      <c r="A556" s="1">
+        <v>555</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C556" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D556" s="1"/>
+    </row>
+    <row r="557" spans="1:4">
+      <c r="A557" s="1">
+        <v>556</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C557" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D557" s="1" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4">
+      <c r="A558" s="1">
+        <v>557</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C558" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D558" s="1" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4">
+      <c r="A559" s="1">
+        <v>558</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C559" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D559" s="1" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4">
+      <c r="A560" s="1">
+        <v>559</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C560" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D560" s="1" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4">
+      <c r="A561" s="1">
+        <v>560</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C561" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D561" s="1" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4">
+      <c r="A562" s="1">
+        <v>561</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C562" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D562" s="1" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4">
+      <c r="A563" s="1">
+        <v>562</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C563" s="1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D563" s="1" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4">
+      <c r="A564" s="1">
+        <v>563</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C564" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D564" s="1" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4">
+      <c r="A565" s="1">
+        <v>564</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C565" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D565" s="1" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4">
+      <c r="A566" s="1">
+        <v>565</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C566" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D566" s="1" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4">
+      <c r="A567" s="1">
+        <v>566</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C567" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D567" s="1" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4">
+      <c r="A568" s="1">
+        <v>567</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C568" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D568" s="1" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4">
+      <c r="A569" s="1">
+        <v>568</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C569" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D569" s="1" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4">
+      <c r="A570" s="1">
+        <v>569</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C570" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D570" s="1" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4">
+      <c r="A571" s="1">
+        <v>570</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C571" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D571" s="1" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4">
+      <c r="A572" s="1">
+        <v>571</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C572" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D572" s="1" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4">
+      <c r="A573" s="1">
+        <v>572</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C573" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D573" s="1" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4">
+      <c r="A574" s="1">
+        <v>573</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C574" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D574" s="1"/>
+    </row>
+    <row r="575" spans="1:4">
+      <c r="A575" s="1">
+        <v>574</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C575" s="1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D575" s="1" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4">
+      <c r="A576" s="1">
+        <v>575</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C576" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D576" s="1" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4">
+      <c r="A577" s="1">
+        <v>576</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C577" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D577" s="1" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4">
+      <c r="A578" s="1">
+        <v>577</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C578" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D578" s="1" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4">
+      <c r="A579" s="1">
+        <v>578</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C579" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D579" s="1" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4">
+      <c r="A580" s="1">
+        <v>579</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C580" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D580" s="1" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4">
+      <c r="A581" s="1">
+        <v>580</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C581" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D581" s="1" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4">
+      <c r="A582" s="1">
+        <v>581</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C582" s="1" t="s">
+        <v>1678</v>
+      </c>
+      <c r="D582" s="1" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4">
+      <c r="A583" s="1">
+        <v>582</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C583" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D583" s="1" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4">
+      <c r="A584" s="1">
+        <v>583</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C584" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D584" s="1" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4">
+      <c r="A585" s="1">
+        <v>584</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D585" s="1"/>
+    </row>
+    <row r="586" spans="1:4">
+      <c r="A586" s="1">
+        <v>585</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C586" s="1" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D586" s="1" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4">
+      <c r="A587" s="1">
+        <v>586</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C587" s="1" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D587" s="1" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4">
+      <c r="A588" s="1">
+        <v>587</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4">
+      <c r="A589" s="1">
+        <v>588</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C589" s="1" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D589" s="1" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4">
+      <c r="A590" s="1">
+        <v>589</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C590" s="1" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D590" s="1" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4">
+      <c r="A591" s="1">
+        <v>590</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C591" s="1" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D591" s="1" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4">
+      <c r="A592" s="1">
+        <v>591</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C592" s="1" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D592" s="1" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4">
+      <c r="A593" s="1">
+        <v>592</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C593" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D593" s="1" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4">
+      <c r="A594" s="1">
+        <v>593</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C594" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D594" s="1"/>
+    </row>
+    <row r="595" spans="1:4">
+      <c r="A595" s="1">
+        <v>594</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C595" s="1" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D595" s="1" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4">
+      <c r="A596" s="1">
+        <v>595</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C596" s="1" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D596" s="1" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4">
+      <c r="A597" s="1">
+        <v>596</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C597" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D597" s="1" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4">
+      <c r="A598" s="1">
+        <v>597</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C598" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D598" s="1" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4">
+      <c r="A599" s="1">
+        <v>598</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C599" s="1" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D599" s="1" t="s">
+        <v>1726</v>
       </c>
     </row>
   </sheetData>
